--- a/KAMCHATKA_REESTR_POSTAVSHIKI/04_Лидер-Энерго_реестр.xlsx
+++ b/KAMCHATKA_REESTR_POSTAVSHIKI/04_Лидер-Энерго_реестр.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -111,6 +116,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,13 +698,37 @@
       <c r="H6" s="7" t="n">
         <v>7625</v>
       </c>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="8" t="n"/>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго»</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>6324029755</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>10876723</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Затвор поворотный дисковый типа ЗПД-150</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -729,13 +761,37 @@
       <c r="H7" s="7" t="n">
         <v>3904</v>
       </c>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго»</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>6324029755</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>10876719</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Затвор поворотный дисковый типа ЗПД-50</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -768,13 +824,37 @@
       <c r="H8" s="7" t="n">
         <v>4209</v>
       </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго»</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>6324029755</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>10876720</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Затвор поворотный дисковый типа ЗПД-80</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:O8"/>
